--- a/jpcore-r4/feature/値1つのみのValueSetを廃止する/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/feature/値1つのみのValueSetを廃止する/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="541">
   <si>
     <t>Property</t>
   </si>
@@ -922,7 +922,10 @@
     <t>second</t>
   </si>
   <si>
-    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。</t>
+    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetは指定しない。</t>
+  </si>
+  <si>
+    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetのバインディングを指定していないことに注意すること。</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
@@ -5361,10 +5364,10 @@
         <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>196</v>
@@ -5451,7 +5454,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>210</v>
@@ -5569,7 +5572,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>217</v>
@@ -5689,7 +5692,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>223</v>
@@ -5811,7 +5814,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>233</v>
@@ -5929,7 +5932,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>235</v>
@@ -6049,7 +6052,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>237</v>
@@ -6094,7 +6097,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6171,7 +6174,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>247</v>
@@ -6291,7 +6294,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>255</v>
@@ -6334,7 +6337,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6411,7 +6414,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>264</v>
@@ -6531,7 +6534,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>272</v>
@@ -6653,7 +6656,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>282</v>
@@ -6775,14 +6778,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6804,16 +6807,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6842,7 +6845,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6860,7 +6863,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6875,30 +6878,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6921,19 +6924,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6982,7 +6985,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6997,19 +7000,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7017,10 +7020,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7043,16 +7046,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7102,7 +7105,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7123,13 +7126,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7137,14 +7140,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7163,19 +7166,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7224,7 +7227,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7239,19 +7242,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7259,14 +7262,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7285,19 +7288,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7346,7 +7349,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7361,19 +7364,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7381,10 +7384,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7407,16 +7410,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7466,7 +7469,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7487,13 +7490,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7501,10 +7504,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7527,19 +7530,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7588,7 +7591,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7603,19 +7606,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7623,10 +7626,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7649,19 +7652,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7686,11 +7689,11 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7708,7 +7711,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7717,7 +7720,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7726,27 +7729,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7772,16 +7775,16 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7806,13 +7809,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7830,7 +7833,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7839,7 +7842,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7854,7 +7857,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7865,14 +7868,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7894,16 +7897,16 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7928,13 +7931,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7952,7 +7955,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7970,27 +7973,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8013,19 +8016,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8074,7 +8077,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8095,10 +8098,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8109,10 +8112,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8138,13 +8141,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8170,13 +8173,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8194,7 +8197,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8212,27 +8215,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8258,16 +8261,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8292,13 +8295,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8316,7 +8319,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8337,10 +8340,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8351,10 +8354,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8377,16 +8380,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8436,7 +8439,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8454,27 +8457,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8497,16 +8500,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8556,7 +8559,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8574,27 +8577,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8617,19 +8620,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8678,7 +8681,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8690,7 +8693,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8699,10 +8702,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8713,10 +8716,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8831,10 +8834,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8951,14 +8954,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8980,10 +8983,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9038,7 +9041,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9073,10 +9076,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9099,13 +9102,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9156,7 +9159,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9165,7 +9168,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9177,10 +9180,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9191,10 +9194,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9217,13 +9220,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9274,7 +9277,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9283,7 +9286,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9295,10 +9298,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9309,10 +9312,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9338,16 +9341,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9375,10 +9378,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9396,7 +9399,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9414,13 +9417,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9431,10 +9434,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9460,16 +9463,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9494,13 +9497,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9518,7 +9521,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9536,13 +9539,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9553,10 +9556,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9579,17 +9582,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9638,7 +9641,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9662,7 +9665,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9673,10 +9676,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9702,10 +9705,10 @@
         <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9756,7 +9759,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9777,10 +9780,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9791,10 +9794,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9817,16 +9820,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9876,7 +9879,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9897,10 +9900,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9911,10 +9914,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9937,16 +9940,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9996,7 +9999,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10017,10 +10020,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10031,10 +10034,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10057,19 +10060,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10118,7 +10121,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10139,10 +10142,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10153,10 +10156,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10271,10 +10274,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10391,14 +10394,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10420,10 +10423,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10478,7 +10481,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10513,10 +10516,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10542,16 +10545,16 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10576,13 +10579,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10600,7 +10603,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10618,16 +10621,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10635,10 +10638,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10661,19 +10664,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10722,7 +10725,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10740,27 +10743,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10786,16 +10789,16 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10820,13 +10823,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10844,7 +10847,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10853,7 +10856,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10868,7 +10871,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10879,14 +10882,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10908,16 +10911,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10942,13 +10945,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10966,7 +10969,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10984,27 +10987,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11030,16 +11033,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11088,7 +11091,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11109,10 +11112,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
